--- a/docs/qa/Skoda-Storyboard-Template-Test-Cases.xlsx
+++ b/docs/qa/Skoda-Storyboard-Template-Test-Cases.xlsx
@@ -9,7 +9,8 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Test Cases" sheetId="3" r:id="rId3"/>
     <sheet name="Test URLs" sheetId="4" r:id="rId4"/>
-    <sheet name="Known Defects" sheetId="5" r:id="rId5"/>
+    <sheet name="New Defects (29 Oct)" sheetId="5" r:id="rId5"/>
+    <sheet name="Known Defects" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$U$126</definedName>
@@ -354,7 +355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -428,24 +429,31 @@
       </c>
       <c r="C2" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A2)</f>
+        <v>27</v>
       </c>
       <c r="D2" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A2,'Test Cases'!$P:$P,"Pass")</f>
+        <v>20</v>
       </c>
       <c r="E2" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A2,'Test Cases'!$P:$P,"Fail")</f>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A2,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A2,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H2" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A2,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str" s="2">
         <f>IF((C2-G2)=0,"",ROUND(D2/(C2-G2)*100,1)&amp;"%")</f>
+        <v>74.1%</v>
       </c>
     </row>
     <row r="3">
@@ -461,24 +469,31 @@
       </c>
       <c r="C3" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A3)</f>
+        <v>8</v>
       </c>
       <c r="D3" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A3,'Test Cases'!$P:$P,"Pass")</f>
+        <v>6</v>
       </c>
       <c r="E3" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A3,'Test Cases'!$P:$P,"Fail")</f>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A3,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A3,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A3,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" t="str" s="2">
         <f>IF((C3-G3)=0,"",ROUND(D3/(C3-G3)*100,1)&amp;"%")</f>
+        <v>75.0%</v>
       </c>
     </row>
     <row r="4">
@@ -494,24 +509,31 @@
       </c>
       <c r="C4" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A4)</f>
+        <v>7</v>
       </c>
       <c r="D4" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A4,'Test Cases'!$P:$P,"Pass")</f>
+        <v>5</v>
       </c>
       <c r="E4" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A4,'Test Cases'!$P:$P,"Fail")</f>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A4,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A4,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A4,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" t="str" s="2">
         <f>IF((C4-G4)=0,"",ROUND(D4/(C4-G4)*100,1)&amp;"%")</f>
+        <v>71.4%</v>
       </c>
     </row>
     <row r="5">
@@ -527,24 +549,31 @@
       </c>
       <c r="C5" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A5)</f>
+        <v>15</v>
       </c>
       <c r="D5" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A5,'Test Cases'!$P:$P,"Pass")</f>
+        <v>10</v>
       </c>
       <c r="E5" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A5,'Test Cases'!$P:$P,"Fail")</f>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A5,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A5,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A5,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str" s="2">
         <f>IF((C5-G5)=0,"",ROUND(D5/(C5-G5)*100,1)&amp;"%")</f>
+        <v>66.7%</v>
       </c>
     </row>
     <row r="6">
@@ -560,24 +589,31 @@
       </c>
       <c r="C6" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A6)</f>
+        <v>8</v>
       </c>
       <c r="D6" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A6,'Test Cases'!$P:$P,"Pass")</f>
+        <v>7</v>
       </c>
       <c r="E6" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A6,'Test Cases'!$P:$P,"Fail")</f>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A6,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A6,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A6,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str" s="2">
         <f>IF((C6-G6)=0,"",ROUND(D6/(C6-G6)*100,1)&amp;"%")</f>
+        <v>87.5%</v>
       </c>
     </row>
     <row r="7">
@@ -593,24 +629,31 @@
       </c>
       <c r="C7" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A7)</f>
+        <v>8</v>
       </c>
       <c r="D7" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A7,'Test Cases'!$P:$P,"Pass")</f>
+        <v>6</v>
       </c>
       <c r="E7" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A7,'Test Cases'!$P:$P,"Fail")</f>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A7,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A7,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H7" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A7,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str" s="2">
         <f>IF((C7-G7)=0,"",ROUND(D7/(C7-G7)*100,1)&amp;"%")</f>
+        <v>75.0%</v>
       </c>
     </row>
     <row r="8">
@@ -626,24 +669,31 @@
       </c>
       <c r="C8" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A8)</f>
+        <v>5</v>
       </c>
       <c r="D8" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A8,'Test Cases'!$P:$P,"Pass")</f>
+        <v>4</v>
       </c>
       <c r="E8" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A8,'Test Cases'!$P:$P,"Fail")</f>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A8,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A8,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H8" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A8,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str" s="2">
         <f>IF((C8-G8)=0,"",ROUND(D8/(C8-G8)*100,1)&amp;"%")</f>
+        <v>80.0%</v>
       </c>
     </row>
     <row r="9">
@@ -659,24 +709,31 @@
       </c>
       <c r="C9" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A9)</f>
+        <v>12</v>
       </c>
       <c r="D9" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A9,'Test Cases'!$P:$P,"Pass")</f>
+        <v>9</v>
       </c>
       <c r="E9" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A9,'Test Cases'!$P:$P,"Fail")</f>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A9,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A9,'Test Cases'!$P:$P,"N/A")</f>
+        <v>1</v>
       </c>
       <c r="H9" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A9,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str" s="2">
         <f>IF((C9-G9)=0,"",ROUND(D9/(C9-G9)*100,1)&amp;"%")</f>
+        <v>81.8%</v>
       </c>
     </row>
     <row r="10">
@@ -692,24 +749,31 @@
       </c>
       <c r="C10" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A10)</f>
+        <v>4</v>
       </c>
       <c r="D10" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A10,'Test Cases'!$P:$P,"Pass")</f>
+        <v>4</v>
       </c>
       <c r="E10" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A10,'Test Cases'!$P:$P,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A10,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A10,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H10" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A10,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str" s="2">
         <f>IF((C10-G10)=0,"",ROUND(D10/(C10-G10)*100,1)&amp;"%")</f>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="11">
@@ -725,24 +789,31 @@
       </c>
       <c r="C11" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A11)</f>
+        <v>5</v>
       </c>
       <c r="D11" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A11,'Test Cases'!$P:$P,"Pass")</f>
+        <v>2</v>
       </c>
       <c r="E11" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A11,'Test Cases'!$P:$P,"Fail")</f>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A11,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>2</v>
       </c>
       <c r="G11" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A11,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H11" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A11,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str" s="2">
         <f>IF((C11-G11)=0,"",ROUND(D11/(C11-G11)*100,1)&amp;"%")</f>
+        <v>40.0%</v>
       </c>
     </row>
     <row r="12">
@@ -758,24 +829,31 @@
       </c>
       <c r="C12" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A12)</f>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A12,'Test Cases'!$P:$P,"Pass")</f>
+        <v>3</v>
       </c>
       <c r="E12" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A12,'Test Cases'!$P:$P,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="F12" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A12,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A12,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A12,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str" s="2">
         <f>IF((C12-G12)=0,"",ROUND(D12/(C12-G12)*100,1)&amp;"%")</f>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="13">
@@ -791,24 +869,31 @@
       </c>
       <c r="C13" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A13)</f>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A13,'Test Cases'!$P:$P,"Pass")</f>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A13,'Test Cases'!$P:$P,"Fail")</f>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A13,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A13,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H13" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A13,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str" s="2">
         <f>IF((C13-G13)=0,"",ROUND(D13/(C13-G13)*100,1)&amp;"%")</f>
+        <v>66.7%</v>
       </c>
     </row>
     <row r="14">
@@ -824,24 +909,31 @@
       </c>
       <c r="C14" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A14)</f>
+        <v>6</v>
       </c>
       <c r="D14" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A14,'Test Cases'!$P:$P,"Pass")</f>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A14,'Test Cases'!$P:$P,"Fail")</f>
+        <v>4</v>
       </c>
       <c r="F14" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A14,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A14,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H14" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A14,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" t="str" s="2">
         <f>IF((C14-G14)=0,"",ROUND(D14/(C14-G14)*100,1)&amp;"%")</f>
+        <v>33.3%</v>
       </c>
     </row>
     <row r="15">
@@ -857,24 +949,31 @@
       </c>
       <c r="C15" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A15)</f>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A15,'Test Cases'!$P:$P,"Pass")</f>
+        <v>0</v>
       </c>
       <c r="E15" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A15,'Test Cases'!$P:$P,"Fail")</f>
+        <v>2</v>
       </c>
       <c r="F15" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A15,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A15,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H15" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A15,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" t="str" s="2">
         <f>IF((C15-G15)=0,"",ROUND(D15/(C15-G15)*100,1)&amp;"%")</f>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="16">
@@ -890,24 +989,31 @@
       </c>
       <c r="C16" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A16)</f>
+        <v>9</v>
       </c>
       <c r="D16" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A16,'Test Cases'!$P:$P,"Pass")</f>
+        <v>4</v>
       </c>
       <c r="E16" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A16,'Test Cases'!$P:$P,"Fail")</f>
+        <v>4</v>
       </c>
       <c r="F16" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A16,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A16,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H16" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A16,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" t="str" s="2">
         <f>IF((C16-G16)=0,"",ROUND(D16/(C16-G16)*100,1)&amp;"%")</f>
+        <v>44.4%</v>
       </c>
     </row>
     <row r="17">
@@ -923,24 +1029,31 @@
       </c>
       <c r="C17" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A17)</f>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A17,'Test Cases'!$P:$P,"Pass")</f>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A17,'Test Cases'!$P:$P,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="F17" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A17,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>2</v>
       </c>
       <c r="G17" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A17,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H17" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A17,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" t="str" s="2">
         <f>IF((C17-G17)=0,"",ROUND(D17/(C17-G17)*100,1)&amp;"%")</f>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="18">
@@ -956,24 +1069,31 @@
       </c>
       <c r="C18" s="2">
         <f>COUNTIF('Test Cases'!$B:$B,$A18)</f>
+        <v>1</v>
       </c>
       <c r="D18" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A18,'Test Cases'!$P:$P,"Pass")</f>
+        <v>0</v>
       </c>
       <c r="E18" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A18,'Test Cases'!$P:$P,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="F18" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A18,'Test Cases'!$P:$P,"Blocked")</f>
+        <v>1</v>
       </c>
       <c r="G18" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A18,'Test Cases'!$P:$P,"N/A")</f>
+        <v>0</v>
       </c>
       <c r="H18" s="2">
         <f>COUNTIFS('Test Cases'!$B:$B,$A18,'Test Cases'!$P:$P,"Not Run")</f>
-      </c>
-      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" t="str" s="2">
         <f>IF((C18-G18)=0,"",ROUND(D18/(C18-G18)*100,1)&amp;"%")</f>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="19">
@@ -985,25 +1105,44 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4">
         <f>SUM(C2:C18)</f>
+        <v>125</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(D2:D18)</f>
+        <v>84</v>
       </c>
       <c r="E19" s="4">
         <f>SUM(E2:E18)</f>
+        <v>33</v>
       </c>
       <c r="F19" s="4">
         <f>SUM(F2:F18)</f>
+        <v>7</v>
       </c>
       <c r="G19" s="4">
         <f>SUM(G2:G18)</f>
+        <v>1</v>
       </c>
       <c r="H19" s="4">
         <f>SUM(H2:H18)</f>
-      </c>
-      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" t="str" s="4">
         <f>IF((C19-G19)=0,"",ROUND(D19/(C19-G19)*100,1)&amp;"%")</f>
-      </c>
+        <v>67.7%</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Run: 29 Oct 2026, main live (aem.live) vs www.skoda-storyboard.com. New defects: see "New Defects (29 Oct)"; existing GitHub defects: see "Known Defects".</t>
+        </is>
+      </c>
+      <c r="B21" s="0"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -1233,17 +1372,33 @@
           <t xml:space="preserve">#74, #85; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O2" s="2"/>
+      <c r="O2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">All 9 template URLs return 200 on main live (home, Media Room, story, press release, model, press kit, series, Images, News). html lang = en-GB on all, = source.</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
+      <c r="S2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
@@ -1324,17 +1479,41 @@
           <t xml:space="preserve">#505, #402; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O3" s="2"/>
+      <c r="O3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/en/, /en/news/, /en/skoda-model/epiq/ → 404 "Page not found" on main; source 200.</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#505 (open), #402</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
@@ -1411,17 +1590,33 @@
           <t xml:space="preserve">#85 (SKODA-1003); header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
+      <c r="O4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/ → 301 → /en. Source redirects by browser language (PO-accepted demo deviation).</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
+      <c r="S4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
@@ -1503,17 +1698,41 @@
           <t xml:space="preserve">#420; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
+      <c r="O5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Main titles have no suffix: "Images", "Epiq", "Media Room"… Source: "Images - Škoda Storyboard" etc. Home "Škoda Storyboard" = source.</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#420 (open)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
@@ -1596,17 +1815,33 @@
           <t xml:space="preserve">SKODA-401; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O6" s="2"/>
+      <c r="O6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">og:image + canonical present on all 9; robots not blocking. Description present on story / PR / model / press kit / series / home; missing on Media Room, Images, News – source has none on these 3 either.</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
+      <c r="S6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
@@ -1686,17 +1921,33 @@
           <t xml:space="preserve">header-megamenu.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
+      <c r="O7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Storyboard menu = source: Models (Fabia…Enyaq, Classic Cars, Concepts) / eMobility / Lifestyle (People, Sports, Adventures) / Škoda World (Innovation &amp; Technology, Design, Responsibility, Corporate Life, Heritage) / Series / Škodapedia / Podcast. Same order.</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="S7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
@@ -1773,17 +2024,41 @@
           <t xml:space="preserve">header-megamenu.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
+      <c r="O8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Header height 108 = source at 375 / 768 / 992 / 1280 / 1440; at 1080 main 108 vs source 172 (source wraps). Menu font Skoda Next 16px / 400 rgb(22, 23, 24) = source.</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#410 (open)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
@@ -1862,17 +2137,33 @@
           <t xml:space="preserve">header-megamenu.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
+      <c r="O9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hover "Models" opens the dropdown and moving away closes it (= source). Keyboard: focusing "Models" opens the dropdown on main (source does not open on focus). Dropdown link Octavia → /en/tag/model/octavia 200, same tab.</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
+      <c r="S9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
@@ -1949,17 +2240,33 @@
           <t xml:space="preserve">header-megamenu.md §3; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
+      <c r="O10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Media Room" → /en/media-room with News / Press Kits / Models / Images / Videos / Company / Škodapedia menu; "Stories" → /en. = source.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
+      <c r="S10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
@@ -2037,17 +2344,41 @@
           <t xml:space="preserve">#71, #365; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
+      <c r="O11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Company submenu = source (9 items). Contacts + Newsletter → demo, same tab (200). Management / Company Logo / Mobile App → source, new tab (pages are preview-only, 404 on live). Brand Group CORE (BGC) → source in a new tab although /en/brand-group-core-bgc is live on the demo (200).</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">To raise</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
@@ -2128,17 +2459,33 @@
           <t xml:space="preserve">mobile-nav.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
+      <c r="O12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">375 and 992: button "Open navigation" (aria-expanded false) → "Close navigation" (true); items Stories / Media Room / Models / eMobility / Lifestyle / Škoda World / Series / Škodapedia / Podcast / Newsletter; Models expands (Fabia visible); Escape closes. Source has the same items (no aria labels).</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
+      <c r="S12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
@@ -2219,17 +2566,33 @@
           <t xml:space="preserve">#499, #83; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
+      <c r="O13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"epiq" → 5 suggestions, all demo paths (/en/emobility/skoda-epiq-…, /en/press-releases/…), click opens in same tab. "stories" → real pages only (/en, /en/category/skoda-world, /en/series-2 …), no nav / footer rows on EN.</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="S13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
@@ -2305,17 +2668,33 @@
           <t xml:space="preserve">SKODA-402; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
+      <c r="O14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Enter → /en/search?filter[search]=epiq&amp;search_type=post, "49 results for “epiq”".</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
+      <c r="S14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
@@ -2394,17 +2773,41 @@
           <t xml:space="preserve">#83, SKODA-303a; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O15" s="2"/>
+      <c r="O15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EN Epiq story: EN plain + CZ / DE / SK / SR links, DE click opens the DE story (de-DE) = source. Other translated stories now carry en + cs alternates (fixed 28 Oct, #83). Home /en and Media Room home show no other language at all; source shows CZ / DE / SK / SR / SL (locale homes not migrated – 404).</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85 (open)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
@@ -2484,17 +2887,33 @@
           <t xml:space="preserve">footer.md, SKODA-304; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O16" s="2"/>
+      <c r="O16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Footer: 40 links on main = 40 on source, same texts and order (Models list, categories, Data Protection, Copyright, Cookies policies, Whistleblower system, RSS, RSS (News)), app badges + Facebook / Instagram / YouTube / WhatsApp.</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
+      <c r="S16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
@@ -2570,17 +2989,33 @@
           <t xml:space="preserve">footer.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O17" s="2"/>
+      <c r="O17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Footer height main = source: 809 / 619 / 830 / 830 / 830 / 830 at 375 / 768 / 992 / 1080 / 1280 / 1440.</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
+      <c r="S17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
@@ -2659,17 +3094,33 @@
           <t xml:space="preserve">footer-mediaroom.md, SKODA-305; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O18" s="2"/>
+      <c r="O18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Media Room footer: h3 Contacts / Subscribe / Company, 12 links, height 706 = source.</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
+      <c r="S18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
@@ -2746,17 +3197,33 @@
           <t xml:space="preserve">footer.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O19" s="2"/>
+      <c r="O19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">375: footer sub-links hidden on both (no toggle on either site); 992+: visible on both. Behaviour = source (no accordion on the source either).</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
+      <c r="S19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
@@ -2837,17 +3304,33 @@
           <t xml:space="preserve">social-share.md, SKODA-215; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O20" s="2"/>
+      <c r="O20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story: dock with "Share this page" → Share on X / Pinterest / LinkedIn / Facebook, and "Scroll to top". Present after scrolling.</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
+      <c r="S20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
@@ -2926,17 +3409,33 @@
           <t xml:space="preserve">media-cart.md; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O21" s="2"/>
+      <c r="O21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story Media Box "+" ×2 → cart badge 2, still 2 after reload, badge opens /en/media-cart. Images listing "+" cannot add (see TC-FL-007).</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
+      <c r="S21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
@@ -3015,17 +3514,37 @@
           <t xml:space="preserve">#363; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O22" s="2"/>
+      <c r="O22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No cookie banner on main (fresh profile); scripts/consent-check.js is a stub that declines by default – the OneTrust CMP is not integrated yet (SKODA-804). Footer "Cookies policies" → skoda-auto.com cookie settings.</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q22" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SKODA-804 (dependency)</t>
+        </is>
+      </c>
       <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
+      <c r="S22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
@@ -3104,17 +3623,33 @@
           <t xml:space="preserve">#85; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O23" s="2"/>
+      <c r="O23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">First Tab → "Skip to content" (href #main, visible); Enter moves focus to &lt;main id="main"&gt;.</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
+      <c r="S23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
@@ -3199,17 +3734,41 @@
           <t xml:space="preserve">AGENTS.md review step 5, #507, #508; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O24" s="2"/>
+      <c r="O24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Home, model page, press kit hub: 0 level mismatches. Story (Epiq): 6 mismatches – Explore more teaser titles h3 on main, h2 on source. Press release: single h1 (spec).</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#507 (open; fix PR #548 open)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
@@ -3292,17 +3851,33 @@
           <t xml:space="preserve">AGENTS.md review step 5; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O25" s="2"/>
+      <c r="O25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">axe-core 4.10 (WCAG 2 A/AA, the Lighthouse a11y engine) on story / PR / model / News: main only color-contrast (5 / 1 / 1 / 3 nodes); source has color-contrast 8–15 + button-name, link-name, aria-input-field-name, link-in-text-block. No new failure on main. Lighthouse itself not run in this pass.</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
+      <c r="S25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
@@ -3388,17 +3963,33 @@
           <t xml:space="preserve">header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O26" s="2"/>
+      <c r="O26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">375: horizontal scroll 0, broken images 0, failed requests 0 on home, story, PR, model, Images, News.</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
+      <c r="S26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
@@ -3478,17 +4069,33 @@
           <t xml:space="preserve">#375, #494; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O27" s="2"/>
+      <c r="O27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">375 (no throttling): CLS 0 on all 6 pages; LCP 64–248 ms. Throttled Lighthouse run not done in this pass.</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
+      <c r="S27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
@@ -3567,17 +4174,33 @@
           <t xml:space="preserve">#485, #499; header-megamenu.md, mobile-nav.md, footer.md, footer-mediaroom.md, language-switcher.md, social-share.md</t>
         </is>
       </c>
-      <c r="O28" s="2"/>
+      <c r="O28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story: 1 link to the source, PR: 3 – none of them point to a page that exists on the demo index. Home / model / Images / News: 0 source links.</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
+      <c r="S28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
@@ -3656,17 +4279,41 @@
           <t xml:space="preserve">template-home.md; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O29" s="2"/>
+      <c r="O29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Promo slider works (Pause rotation button, slides change). Slides differ: main "Meet the Peaq: Intuitive…" / "Epiq Now Dresses Up in Sportline…" / "Peaq Inside a DesignBlok"; source "“Never Stop Fighting…” Robert Virves" / "The world beneath the upholstery" / "Kodiaq Celebrates 10 Years…" (newer items not migrated).</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#342 / #447 (content refresh)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
@@ -3744,17 +4391,33 @@
           <t xml:space="preserve">stories.md, SKODA-214; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O30" s="2"/>
+      <c r="O30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Load more = source: 5 → 11 → 17 cards on both. First cards differ only because of content freshness (see TC-HM-008).</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
+      <c r="S30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
@@ -3832,17 +4495,33 @@
           <t xml:space="preserve">carousel-rails.md, #361; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O31" s="2"/>
+      <c r="O31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">eMobility / Lifestyle / Škoda World rails: h3 = source, 10 cards each, Next keeps its position (1222,434) after click, 0 empty arrows.</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
+      <c r="S31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
@@ -3919,17 +4598,33 @@
           <t xml:space="preserve">template-home.md; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O32" s="2"/>
+      <c r="O32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Model tiles Elroq, Kodiaq, Enyaq, Karoq, Kamiq, Scala, Fabia, Superb, Octavia, Epiq, Peaq = source order; links /en/tag/model/… 200.</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
+      <c r="S32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
@@ -4006,17 +4701,33 @@
           <t xml:space="preserve">P4 note: handle is span on main, h3 on source; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O33" s="2"/>
+      <c r="O33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">@skodaglobal / @skodagram / @skoda open in a new tab = source. Handles are span on main, h3 on source (P4 PO decision).</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
+      <c r="S33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
@@ -4092,17 +4803,33 @@
           <t xml:space="preserve">card-teaser.md; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O34" s="2"/>
+      <c r="O34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Card title Skoda Next 29.6px / 35.52px / 400 = source; date format dd. m. yyyy = source.</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
+      <c r="S34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
@@ -4179,17 +4906,33 @@
           <t xml:space="preserve">template-home.md; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O35" s="2"/>
+      <c r="O35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same sections and order; height 4734 = 4734 at 1280.</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
+      <c r="S35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
@@ -4265,17 +5008,41 @@
           <t xml:space="preserve">#342, #447; template-home.md, stories.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O36" s="2"/>
+      <c r="O36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Newest card main 15. 10. 2026, source 29. 10. 2026. Media feed build b-b8b032bbe7 not rebuilt; index newest 20 Oct.</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#342 / #447 (open)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
@@ -4352,17 +5119,41 @@
           <t xml:space="preserve">template-home.md; template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O37" s="2"/>
+      <c r="O37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Promo differs: main "Škoda expands electric portfolio…", "Classic Days 2026 - Press Kit", "Epiq Sportline debuts…"; source "Škoda Auto promotes diversity…", "…extends partnership with the Czech Phil…", "Kodiaq range expands…" (content freshness).</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
-      <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#342 / #447 (open)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
@@ -4440,17 +5231,33 @@
           <t xml:space="preserve">carousel-rails.md; template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O38" s="2"/>
+      <c r="O38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">News rail h3, cards with dates (5. 10. / 25. 9. 2026), arrows work; links open on the demo. Newest items differ from source (freshness).</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
+      <c r="S38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
@@ -4527,17 +5334,37 @@
           <t xml:space="preserve">#466; template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O39" s="2"/>
+      <c r="O39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verified 28 Oct (#466 closed): 0 partial 3rd lines at 390 / 768 / 992 / 1080; card size = source. No code change since.</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q39" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#466 (closed)</t>
+        </is>
+      </c>
       <c r="R39" s="2"/>
-      <c r="S39" s="2"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
+      <c r="S39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
@@ -4615,17 +5442,41 @@
           <t xml:space="preserve">media-cart.md, downloads.md; template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O40" s="2"/>
+      <c r="O40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Download menu works (Original + 1920px, files 200). "+" (add to cart) on rail cards does not add anything: badge stays empty, cart stays empty.</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-01 (to raise)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
@@ -4704,17 +5555,33 @@
           <t xml:space="preserve">gallery-lightbox.md; template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O41" s="2"/>
+      <c r="O41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Images rail card → gallery overlay "1 / 10", → key "2 / 10", Escape closes, focus back on the card link.</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
+      <c r="S41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
@@ -4790,17 +5657,33 @@
           <t xml:space="preserve">template-home.md; template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O42" s="2"/>
+      <c r="O42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Press Kits band background rgb(14, 58, 47) = #0e3a2f, full width 0 + 1280.</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
+      <c r="S42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
@@ -4876,17 +5759,33 @@
           <t xml:space="preserve">template-home.md, carousel-rails.md, card-teaser.md</t>
         </is>
       </c>
-      <c r="O43" s="2"/>
+      <c r="O43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heights main / source: 3826 / 3825 (375), 3254 / 3253 (768), 3173 / 3172 (992), 3478 / 3477 (1280, 1440). Section headings h3 = source.</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
-      <c r="S43" s="2"/>
-      <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
+      <c r="S43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
@@ -4965,17 +5864,33 @@
           <t xml:space="preserve">story-detail.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O44" s="2"/>
+      <c r="O44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hero image 989×557 = source; h1 Skoda Next 40px / 44px / 600 rgb(22, 23, 24) = source; date 15. 9. 2026 = source.</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
-      <c r="S44" s="2"/>
-      <c r="T44" s="2"/>
-      <c r="U44" s="2"/>
+      <c r="S44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
@@ -5052,17 +5967,33 @@
           <t xml:space="preserve">_TEMPLATES.md shared shell; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O45" s="2"/>
+      <c r="O45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1280: text column 26 + 819 = source; sidebar 845 + 419 (source 845 + 409, +10px). 375: one column 10 + 355 = source.</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
-      <c r="S45" s="2"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
+      <c r="S45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
@@ -5138,17 +6069,33 @@
           <t xml:space="preserve">story-detail.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O46" s="2"/>
+      <c r="O46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Perex Skoda Next 20px / 30px / 600, margin-bottom 8px = source.</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
+      <c r="S46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
@@ -5228,17 +6175,37 @@
           <t xml:space="preserve">story-image-carousel.md, #361, #456; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O47" s="2"/>
+      <c r="O47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Next image" moves one slide; no slide change after 7 s; no pause button (accepted deviation #361).</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q47" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#361 (closed)</t>
+        </is>
+      </c>
       <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
+      <c r="S47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
@@ -5314,17 +6281,41 @@
           <t xml:space="preserve">Open defect (sweep 29 Oct); story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O48" s="2"/>
+      <c r="O48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">375: every slide 215px tall on 20 / 20 stories; source keeps each image ratio (182–337px, e.g. Epiq 255 / 259 / 215 / 287 / 261 / 288).</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-07 (to raise)</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
@@ -5401,17 +6392,33 @@
           <t xml:space="preserve">gallery-lightbox.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O49" s="2"/>
+      <c r="O49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Clicking a slider image opens no lightbox on main and on source (same behaviour).</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
+      <c r="S49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
@@ -5487,17 +6494,33 @@
           <t xml:space="preserve">embeds.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O50" s="2"/>
+      <c r="O50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Graffiti story: YouTube embed – click loads the YouTube iframe with autoplay.</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
+      <c r="S50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
@@ -5573,17 +6596,33 @@
           <t xml:space="preserve">highlight.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O51" s="2"/>
+      <c r="O51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Highlight panel rgb(14, 58, 47), 839px wide, text 24px / 300 white = source. Padding box differs (main 42 / 10px, source 32 / 0px) – visual offset not measured.</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
+      <c r="S51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
@@ -5661,17 +6700,41 @@
           <t xml:space="preserve">Open defect (sweep 29 Oct); story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O52" s="2"/>
+      <c r="O52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Author name 13.33px / 400 on main, 16px / 600 on source (Peaq comfort "Radim Doričák", graffiti "Meredith Kelly").</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="2"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-08 (to raise)</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
@@ -5750,17 +6813,41 @@
           <t xml:space="preserve">#507, #508; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O53" s="2"/>
+      <c r="O53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Explore more section h3 = source, but teaser titles h3 on main vs h2 on source (19 stories). Sunroof story: Explore more / Tags / Media Box / Related Stories h2 vs h3.</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#507 (open, fix PR #548), #508 (open)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
@@ -5836,17 +6923,33 @@
           <t xml:space="preserve">tags.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O54" s="2"/>
+      <c r="O54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Tags 2026 / Epiq = source; /en/tag/years/2026 → 200 on the demo.</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
-      <c r="S54" s="2"/>
-      <c r="T54" s="2"/>
-      <c r="U54" s="2"/>
+      <c r="S54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
@@ -5929,17 +7032,41 @@
           <t xml:space="preserve">#293, #295, downloads.md; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O55" s="2"/>
+      <c r="O55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Band 0 + 1280 / 0 + 1440 on 20 / 20 stories (#293 fixed). Dates = source on 19 / 20; Sunroof story 0 / 10 (source 10 / 10). Cart "+" adds (badge 1 / 2, 19 files for "add all"). Wireless story title shows part of a 3rd line (#295).</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-      <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-06 (to raise), #295 (open)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
@@ -6019,17 +7146,41 @@
           <t xml:space="preserve">#293, #506; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O56" s="2"/>
+      <c r="O56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Related Stories band full width on 18 stories. Slavia story: band missing (source 4 cards, page −354px). Kylaq story has no band on either site.</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="2"/>
-      <c r="T56" s="2"/>
-      <c r="U56" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#506 (open)</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
@@ -6109,17 +7260,33 @@
           <t xml:space="preserve">#485, #365; story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O57" s="2"/>
+      <c r="O57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EN story newsletter card = source (Subscribe now!, consent link, Manage subscription → source). Not added on DE stories (as source).</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
-      <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
+      <c r="S57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
@@ -6195,17 +7362,33 @@
           <t xml:space="preserve">story-detail.md, story-image-carousel.md, highlight.md, tags.md, downloads.md</t>
         </is>
       </c>
-      <c r="O58" s="2"/>
+      <c r="O58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Section order = source. Height Δ at 1280 (content only): Epiq +126, Peaq record +78, practical Epiq +110, Slavia −354 (#506), graffiti +161.</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-      <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
+      <c r="S58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
@@ -6283,17 +7466,33 @@
           <t xml:space="preserve">template-press-release.md, SKODA-607; template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O59" s="2"/>
+      <c r="O59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No hero; h1 26px / 32.5px / 600 rgb(10, 10, 10) = source; date 11px / 600 rgb(118, 118, 118) above the h1; lead bold (strong 600 on main, p 600 on source – same look).</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
+      <c r="S59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
@@ -6370,17 +7569,33 @@
           <t xml:space="preserve">#386; template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O60" s="2"/>
+      <c r="O60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Body paragraphs 16px / 24px / 400 rgb(22, 23, 24) = source; bold sub-heads strong 600 = source.</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="2"/>
+      <c r="S60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
@@ -6456,17 +7671,33 @@
           <t xml:space="preserve">highlight.md; template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O61" s="2"/>
+      <c r="O61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Zellmer PR grey callout (FAQ): background rgb(243, 243, 243), padding 25px, width 812px, text 16px / 24px / 400 = source.</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
-      <c r="S61" s="2"/>
-      <c r="T61" s="2"/>
-      <c r="U61" s="2"/>
+      <c r="S61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
@@ -6545,17 +7776,41 @@
           <t xml:space="preserve">#274, downloads.md; template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O62" s="2"/>
+      <c r="O62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Media Box dates 2 / 2, 5 / 5, 4 / 4 = source; band 0 + 1280; image "+" adds to cart and files download (200). PDF card icon: 48px grey (#C4C6C7) on main vs 64×52 white on source, as measured 27–28 Oct – no code change since; the automated probe could not read the icon today (CSS pseudo-element), so confirm by eye.</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
-      <c r="T62" s="2"/>
-      <c r="U62" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#274 (closed – reopen)</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
@@ -6631,17 +7886,33 @@
           <t xml:space="preserve">template-press-release.md; template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O63" s="2"/>
+      <c r="O63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Tags and newsletter box present in the secondary column = source.</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
+      <c r="S63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
@@ -6720,17 +7991,33 @@
           <t xml:space="preserve">template-press-release.md; template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O64" s="2"/>
+      <c r="O64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Related Press Releases dark band full width; "Based on tags" line = source.</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
-      <c r="T64" s="2"/>
-      <c r="U64" s="2"/>
+      <c r="S64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
@@ -6806,17 +8093,33 @@
           <t xml:space="preserve">template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O65" s="2"/>
+      <c r="O65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Two columns at 1280; one column at 375 = source.</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
-      <c r="T65" s="2"/>
-      <c r="U65" s="2"/>
+      <c r="S65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
@@ -6894,17 +8197,33 @@
           <t xml:space="preserve">template-press-release.md, downloads.md, highlight.md</t>
         </is>
       </c>
-      <c r="O66" s="2"/>
+      <c r="O66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1280 heights: Zellmer 3900 / 3899, National Theatre 4114 / 4113, Board 3646 / 3645, 936 km 4377 / 4420 (−43). Single h1 (spec).</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
+      <c r="S66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
@@ -6982,17 +8301,33 @@
           <t xml:space="preserve">template-model-page.md, SKODA-208; template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O67" s="2"/>
+      <c r="O67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Hero h1 36px / 45px / 700 white = source on 5 models; no hero arrows on either site.</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
+      <c r="S67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
@@ -7069,17 +8404,33 @@
           <t xml:space="preserve">template-model-page.md; template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O68" s="2"/>
+      <c r="O68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">8 anchors = source (Model Description, Key Facts, Technical Data, News, Press Kits, Stories, Images, Videos); "Technical Data" click scrolls to the section (99px from top). Still visible at 768 on both.</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
+      <c r="S68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
@@ -7157,17 +8508,37 @@
           <t xml:space="preserve">#495; template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O69" s="2"/>
+      <c r="O69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Epiq: Model Description, Highlights, Technical Data present (h2) = source.</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q69" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#495</t>
+        </is>
+      </c>
       <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
-      <c r="T69" s="2"/>
-      <c r="U69" s="2"/>
+      <c r="S69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
@@ -7248,17 +8619,41 @@
           <t xml:space="preserve">template-model-page.md, open sweep defect (Superb); template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O70" s="2"/>
+      <c r="O70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Superb: News 8 (source 10), Press Kits 7 (source 10), "Škoda Superb Sportline | Footage 9:16" missing. Octavia / Fabia heights equal.</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="2"/>
-      <c r="U70" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-09 (to raise)</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
@@ -7337,17 +8732,41 @@
           <t xml:space="preserve">#466; template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O71" s="2"/>
+      <c r="O71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Title clamp verified 28 Oct (#466). "+" on media rails cannot add to cart (same as NEW-01).</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-01 (to raise)</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
@@ -7423,17 +8842,37 @@
           <t xml:space="preserve">P4 PO decision; template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O72" s="2"/>
+      <c r="O72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Rails EN only; source mixes SK / SR items (PO decision).</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q72" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P4 PO decision</t>
+        </is>
+      </c>
       <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
+      <c r="S72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
@@ -7513,17 +8952,33 @@
           <t xml:space="preserve">template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O73" s="2"/>
+      <c r="O73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heights: Superb 6974 = 6974, Octavia 7127 = 7127, Fabia 5298 = 5298, Epiq 6384 / 6458 (−74), Peaq 6627 / 6701 (−74, known). h1 = source.</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
-      <c r="T73" s="2"/>
-      <c r="U73" s="2"/>
+      <c r="S73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
@@ -7599,17 +9054,33 @@
           <t xml:space="preserve">template-model-page.md, carousel-rails.md</t>
         </is>
       </c>
-      <c r="O74" s="2"/>
+      <c r="O74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/en/skoda-model/elroq/elroq-rs → 200.</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
-      <c r="T74" s="2"/>
-      <c r="U74" s="2"/>
+      <c r="S74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
@@ -7687,17 +9158,33 @@
           <t xml:space="preserve">SKODA-209; template-category-archive.md</t>
         </is>
       </c>
-      <c r="O75" s="2"/>
+      <c r="O75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">h1 "eMobility" / "Lifestyle Adventures" / "Models Elroq" / "Years 2026" present.</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
+      <c r="S75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
@@ -7774,17 +9261,33 @@
           <t xml:space="preserve">template-category-archive.md; template-category-archive.md</t>
         </is>
       </c>
-      <c r="O76" s="2"/>
+      <c r="O76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">eMobility: same 6 first cards and dates as source; columns 3 / 2 / 1 at 1280 / 768 / 375 = source.</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-      <c r="T76" s="2"/>
-      <c r="U76" s="2"/>
+      <c r="S76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
@@ -7860,17 +9363,33 @@
           <t xml:space="preserve">template-category-archive.md</t>
         </is>
       </c>
-      <c r="O77" s="2"/>
+      <c r="O77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Load more 6 → 12 (category), 4 → 10 (tag Elroq) = source.</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-      <c r="T77" s="2"/>
-      <c r="U77" s="2"/>
+      <c r="S77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
@@ -7948,17 +9467,41 @@
           <t xml:space="preserve">template-category-archive.md</t>
         </is>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Lifestyle › Adventures: source starts with "Sand, heat, and camels…" (17. 3. 2026) and "Giant spa towers, gingerbread…" (5. 2. 2026); main starts with "A journey you will never forget" – the 2 stories are not migrated.</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-12 (to raise)</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
@@ -8036,17 +9579,33 @@
           <t xml:space="preserve">template-category-archive.md; template-category-archive.md</t>
         </is>
       </c>
-      <c r="O79" s="2"/>
+      <c r="O79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Tag Elroq = source (La dolce vita…, 30. 7. 2026). Tag 2026: source newest 29. 10. 2026, main 15. 10. 2026 (freshness #342 / #447).</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
+      <c r="S79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
@@ -8122,17 +9681,41 @@
           <t xml:space="preserve">SKODA-402; faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O80" s="2"/>
+      <c r="O80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">News: 6 cards + Load more = source layout; newest main 12. 10. 2026 vs source 27. 10. 2026 (freshness).</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-      <c r="T80" s="2"/>
-      <c r="U80" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#342 / #447 (open)</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
@@ -8210,17 +9793,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O81" s="2"/>
+      <c r="O81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Oldest → first 27. 9. 2018, URL ?sortby=oldest; Newest restores 12. 10. 2026. Images: Oldest re-sorts.</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" s="2"/>
-      <c r="S81" s="2"/>
-      <c r="T81" s="2"/>
-      <c r="U81" s="2"/>
+      <c r="S81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
@@ -8296,17 +9895,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O82" s="2"/>
+      <c r="O82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EN News has no in-listing search box on main or source; site search covered by TC-FL-009.</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
-      <c r="T82" s="2"/>
-      <c r="U82" s="2"/>
+      <c r="S82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
@@ -8386,17 +10001,33 @@
           <t xml:space="preserve">faceted-listing.md; faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O83" s="2"/>
+      <c r="O83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Advanced filter → Model → Superb: "Advanced filter (1)", URL filter[model][]=superb, first card "Škoda Superb: 25 years…" = source for the same filter. Clear not exercised.</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" s="2"/>
-      <c r="S83" s="2"/>
-      <c r="T83" s="2"/>
-      <c r="U83" s="2"/>
+      <c r="S83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
@@ -8472,17 +10103,33 @@
           <t xml:space="preserve">#485; faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O84" s="2"/>
+      <c r="O84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/en/search?filter[search]=zzqxw → "No results for “zzqxw”".</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
-      <c r="S84" s="2"/>
-      <c r="T84" s="2"/>
-      <c r="U84" s="2"/>
+      <c r="S84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
@@ -8562,17 +10209,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O85" s="2"/>
+      <c r="O85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Load more 6 → 12 on News, Press Kits, categories; Images 12 per page.</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
-      <c r="T85" s="2"/>
-      <c r="U85" s="2"/>
+      <c r="S85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
@@ -8650,17 +10313,41 @@
           <t xml:space="preserve">gallery-lightbox.md, media-cart.md; faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O86" s="2"/>
+      <c r="O86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Lightbox "1 / 12" → "2 / 12", Escape closes, focus back on the card. Download Original / 1920px → files 200 (PNG downloaded). "+" add to cart: only "1920px" and it is disabled (aria-disabled), so nothing can be added from Images / Videos.</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2"/>
-      <c r="T86" s="2"/>
-      <c r="U86" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-01 (to raise)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
@@ -8737,17 +10424,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O87" s="2"/>
+      <c r="O87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Videos: card opens the overlay with the Vimeo iframe (autoplay), "1 / 12" → "2 / 12".</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
+      <c r="S87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
@@ -8824,17 +10527,33 @@
           <t xml:space="preserve">SKODA-402; faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O88" s="2"/>
+      <c r="O88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/en/search?filter[search]=epiq → "49 results for “epiq”" (= header search). Source result count not parsed.</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
+      <c r="S88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
@@ -8910,17 +10629,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O89" s="2"/>
+      <c r="O89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Filter Superb kept after reload and after opening a card and pressing Back.</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-      <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
+      <c r="S89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
@@ -8996,17 +10731,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O90" s="2"/>
+      <c r="O90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Press Kits: first 3 = source (Classic Days 2026, Peaq, Epiq), Load more 6 → 12.</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
-      <c r="T90" s="2"/>
-      <c r="U90" s="2"/>
+      <c r="S90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
@@ -9084,17 +10835,33 @@
           <t xml:space="preserve">faceted-listing.md, media-cart.md, gallery-lightbox.md</t>
         </is>
       </c>
-      <c r="O91" s="2"/>
+      <c r="O91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Images / Videos 2140 / 2139 at 1280; News 1606 / 1579 (+27, content); columns 3 / 2 / 1 = source.</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
-      <c r="T91" s="2"/>
-      <c r="U91" s="2"/>
+      <c r="S91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
@@ -9171,17 +10938,33 @@
           <t xml:space="preserve">media-cart.md; media-cart.md</t>
         </is>
       </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">After 2 "+" from a story Media Box: "2 / 80 files · 3.7 MB", both items listed.</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
-      <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
+      <c r="S92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
@@ -9258,17 +11041,33 @@
           <t xml:space="preserve">media-cart.md</t>
         </is>
       </c>
-      <c r="O93" s="2"/>
+      <c r="O93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Remove → "1 / 80 files · 2.8 MB"; badge and list update.</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
-      <c r="T93" s="2"/>
-      <c r="U93" s="2"/>
+      <c r="S93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
@@ -9345,17 +11144,33 @@
           <t xml:space="preserve">media-cart.md</t>
         </is>
       </c>
-      <c r="O94" s="2"/>
+      <c r="O94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Download package" → skoda-storyboard-media-2026-10-29.zip (no failure).</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
-      <c r="S94" s="2"/>
-      <c r="T94" s="2"/>
-      <c r="U94" s="2"/>
+      <c r="S94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
@@ -9431,17 +11246,33 @@
           <t xml:space="preserve">media-cart.md</t>
         </is>
       </c>
-      <c r="O95" s="2"/>
+      <c r="O95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Empty package" → "0 / 80 files · 0 B … No downloads".</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
-      <c r="S95" s="2"/>
-      <c r="T95" s="2"/>
-      <c r="U95" s="2"/>
+      <c r="S95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
@@ -9518,17 +11349,37 @@
           <t xml:space="preserve">#71 (SKODA-810); company-pages.md, template-page-base.md</t>
         </is>
       </c>
-      <c r="O96" s="2"/>
+      <c r="O96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Contacts: height 5499 / 5503, 12 mailto, 5 LinkedIn, 13 portraits = source (main also links 10 phone numbers).</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q96" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#71</t>
+        </is>
+      </c>
       <c r="R96" s="2"/>
-      <c r="S96" s="2"/>
-      <c r="T96" s="2"/>
-      <c r="U96" s="2"/>
+      <c r="S96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
@@ -9607,17 +11458,37 @@
           <t xml:space="preserve">#71; company-pages.md, template-page-base.md</t>
         </is>
       </c>
-      <c r="O97" s="2"/>
+      <c r="O97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Preview: height 3619 = source, 8 headings, 7 images (toggles / lightbox verified 28 Oct on #71). Not published on live (404).</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q97" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#71 – publish after DAM PDF ingest</t>
+        </is>
+      </c>
       <c r="R97" s="2"/>
-      <c r="S97" s="2"/>
-      <c r="T97" s="2"/>
-      <c r="U97" s="2"/>
+      <c r="S97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
@@ -9694,17 +11565,37 @@
           <t xml:space="preserve">#71; company-pages.md, template-page-base.md</t>
         </is>
       </c>
-      <c r="O98" s="2"/>
+      <c r="O98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Preview: 18 tiles, 38 links, height 2365 = source. Not published on live (404).</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q98" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#71 – publish after DAM PDF ingest</t>
+        </is>
+      </c>
       <c r="R98" s="2"/>
-      <c r="S98" s="2"/>
-      <c r="T98" s="2"/>
-      <c r="U98" s="2"/>
+      <c r="S98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
@@ -9781,17 +11672,41 @@
           <t xml:space="preserve">#71; company-pages.md, template-page-base.md</t>
         </is>
       </c>
-      <c r="O99" s="2"/>
+      <c r="O99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Preview: height 2963 = source, 8 images, 2 store links. h1 "Škoda Media Room:new mobile app" (missing space; source "Room: new"). Not published on live.</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" s="2"/>
-      <c r="S99" s="2"/>
-      <c r="T99" s="2"/>
-      <c r="U99" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#71 (dev 8)</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P4</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
@@ -9867,17 +11782,37 @@
           <t xml:space="preserve">#365; company-pages.md, template-page-base.md</t>
         </is>
       </c>
-      <c r="O100" s="2"/>
+      <c r="O100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Newsletter: height 1677 = source, 7 images; Media Room menu link opens it (200).</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q100" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#365</t>
+        </is>
+      </c>
       <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
-      <c r="T100" s="2"/>
-      <c r="U100" s="2"/>
+      <c r="S100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
@@ -9960,17 +11895,37 @@
           <t xml:space="preserve">SKODA-813, #363; template-page-base.md</t>
         </is>
       </c>
-      <c r="O101" s="2"/>
+      <c r="O101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Copyright 2048 = 2048, Impressum 1178 = 1178, Cookies 6020 = 6020 (24 headings), Terms 3052 / 3136 (−84, approved deviation on #363). Links equal.</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q101" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#363</t>
+        </is>
+      </c>
       <c r="R101" s="2"/>
-      <c r="S101" s="2"/>
-      <c r="T101" s="2"/>
-      <c r="U101" s="2"/>
+      <c r="S101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
@@ -10051,17 +12006,37 @@
           <t xml:space="preserve">#363; template-page-base.md</t>
         </is>
       </c>
-      <c r="O102" s="2"/>
+      <c r="O102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">IIHF terms / picture-guidelines 200 (verified 28 Oct: /en/iihf, /lv, /ru → 301 to the hockey story).</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q102" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#363</t>
+        </is>
+      </c>
       <c r="R102" s="2"/>
-      <c r="S102" s="2"/>
-      <c r="T102" s="2"/>
-      <c r="U102" s="2"/>
+      <c r="S102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
@@ -10137,17 +12112,33 @@
           <t xml:space="preserve">#74; template-page-base.md</t>
         </is>
       </c>
-      <c r="O103" s="2"/>
+      <c r="O103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Shell equal (heights above).</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
-      <c r="S103" s="2"/>
-      <c r="T103" s="2"/>
-      <c r="U103" s="2"/>
+      <c r="S103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
@@ -10223,17 +12214,41 @@
           <t xml:space="preserve">SKODA-207; series.md</t>
         </is>
       </c>
-      <c r="O104" s="2"/>
+      <c r="O104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Main shows 25 series cards, source 24: extra "Explorers of sustainability" card on main (+30px).</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" s="2"/>
-      <c r="S104" s="2"/>
-      <c r="T104" s="2"/>
-      <c r="U104" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-11 (to raise)</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
@@ -10312,17 +12327,33 @@
           <t xml:space="preserve">series.md, SKODA-221; series.md</t>
         </is>
       </c>
-      <c r="O105" s="2"/>
+      <c r="O105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1280: h1 48px / 300 white over a 556px band = source (61.8vh). 375: image then ink 48px caption on white = source.</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" s="2"/>
-      <c r="S105" s="2"/>
-      <c r="T105" s="2"/>
-      <c r="U105" s="2"/>
+      <c r="S105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
@@ -10405,17 +12436,33 @@
           <t xml:space="preserve">series.md; series.md</t>
         </is>
       </c>
-      <c r="O106" s="2"/>
+      <c r="O106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">130 years 3182 = 3182 (14 tiles), 125 years 2662 = 2662 (8), Unexpected jobs 2038 = 2038 (5), Roads &amp; Places / Minutes = 0px (sweep).</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
-      <c r="S106" s="2"/>
-      <c r="T106" s="2"/>
-      <c r="U106" s="2"/>
+      <c r="S106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
@@ -10495,17 +12542,41 @@
           <t xml:space="preserve">SKODA-805, open sweep defect (Epiq Sportline); press-kit-template.md, press-kit-media.md, press-kit-variant.md, faq-accordion.md</t>
         </is>
       </c>
-      <c r="O107" s="2"/>
+      <c r="O107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Epiq hub: "Škoda Epiq Sportline" tile missing (source has it before FAQ). Peaq and Motorsport hubs = source.</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" s="2"/>
-      <c r="S107" s="2"/>
-      <c r="T107" s="2"/>
-      <c r="U107" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-03 (to raise)</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
@@ -10583,17 +12654,41 @@
           <t xml:space="preserve">press-kit-template.md, press-kit-media.md, press-kit-variant.md, faq-accordion.md</t>
         </is>
       </c>
-      <c r="O108" s="2"/>
+      <c r="O108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WhatsApp → go.skoda.eu/whatsapp = source. ZIP: Peaq = source (…/2026/09/Skoda_Peaq_323f2835.zip, 200). Epiq main …/2026/08/Skoda_Epiq_c5a5f2fe.zip vs source …/2026/10/Skoda_Epiq_f59cece2.zip (older package).</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" s="2"/>
-      <c r="S108" s="2"/>
-      <c r="T108" s="2"/>
-      <c r="U108" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-04 (to raise)</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
@@ -10669,17 +12764,41 @@
           <t xml:space="preserve">Open sweep defect; press-kit-template.md, press-kit-media.md, press-kit-variant.md, faq-accordion.md</t>
         </is>
       </c>
-      <c r="O109" s="2"/>
+      <c r="O109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Peaq first-glimpse Media Box band 16 + 1248 at 1280, 96 + 1248 at 1440 (source 0 + 1280 / 0 + 1440).</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" s="2"/>
-      <c r="S109" s="2"/>
-      <c r="T109" s="2"/>
-      <c r="U109" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-05 (to raise)</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
@@ -10758,17 +12877,41 @@
           <t xml:space="preserve">SKODA-806–808; press-kit-template.md, press-kit-media.md, press-kit-variant.md, faq-accordion.md</t>
         </is>
       </c>
-      <c r="O110" s="2"/>
+      <c r="O110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Peaq Technical data: 1694 / 1823px, 2 vs 5 headings, 1 vs 4 images. Epiq FAQ chapter: 1606 / 1875px, 7 vs 10 headings, 0 vs 3 images.</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" s="2"/>
-      <c r="S110" s="2"/>
-      <c r="T110" s="2"/>
-      <c r="U110" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEW-10 (to raise); SKODA-852 PR #546 open</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
@@ -10844,17 +12987,33 @@
           <t xml:space="preserve">faq-accordion.md; press-kit-template.md, press-kit-media.md, press-kit-variant.md, faq-accordion.md</t>
         </is>
       </c>
-      <c r="O111" s="2"/>
+      <c r="O111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Epiq FAQ: click toggles aria-expanded false → true; Enter opens, Space closes on the next question.</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
-      <c r="S111" s="2"/>
-      <c r="T111" s="2"/>
-      <c r="U111" s="2"/>
+      <c r="S111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
@@ -10932,17 +13091,33 @@
           <t xml:space="preserve">press-kit-media.md; press-kit-template.md, press-kit-media.md, press-kit-variant.md, faq-accordion.md</t>
         </is>
       </c>
-      <c r="O112" s="2"/>
+      <c r="O112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Peaq Videos chapter 7446 / 7435, 13 headings, 11 media = source; infographics 200.</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
-      <c r="S112" s="2"/>
-      <c r="T112" s="2"/>
-      <c r="U112" s="2"/>
+      <c r="S112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
@@ -11020,17 +13195,41 @@
           <t xml:space="preserve">#76, SKODA-706; template-404.md</t>
         </is>
       </c>
-      <c r="O113" s="2"/>
+      <c r="O113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HTTP 404 with header + footer, but only "Page not found / Or return to the homepage." The two variant fragments (/en/fragments/404/youve-reached-a-dead-end, …/welcome-to-our-remote-car-park) are 200 on preview, 404 on live. Source: "Welcome to our remote car park…".</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" s="2"/>
-      <c r="S113" s="2"/>
-      <c r="T113" s="2"/>
-      <c r="U113" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#76 (closed – reopen / publish)</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
@@ -11106,17 +13305,41 @@
           <t xml:space="preserve">#76; template-404.md</t>
         </is>
       </c>
-      <c r="O114" s="2"/>
+      <c r="O114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/en/does%20not%20exist → plain-text "404 Not Found" (no header / footer).</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" s="2"/>
-      <c r="S114" s="2"/>
-      <c r="T114" s="2"/>
-      <c r="U114" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#76 (closed – reopen)</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr" s="2">
@@ -11198,17 +13421,37 @@
           <t xml:space="preserve">#85, #485; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O115" s="2"/>
+      <c r="O115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CS / DE / SK / SR menus and footers = source (Modely / Modelle / Modely / Modeli), html lang cs-CZ / de-DE / sk-SK / sr-RS (verified 28 Oct 12:05 UTC; no deploy since).</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q115" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85</t>
+        </is>
+      </c>
       <c r="R115" s="2"/>
-      <c r="S115" s="2"/>
-      <c r="T115" s="2"/>
-      <c r="U115" s="2"/>
+      <c r="S115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
@@ -11286,17 +13529,41 @@
           <t xml:space="preserve">#85; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O116" s="2"/>
+      <c r="O116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CS "Odebírat články" = source; SK "Odber noviniek" still missing (/sk/nav). Fix in PR #543 (open) + SK nav re-push.</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" s="2"/>
-      <c r="S116" s="2"/>
-      <c r="T116" s="2"/>
-      <c r="U116" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85 (open; fix PR #543)</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
@@ -11373,17 +13640,37 @@
           <t xml:space="preserve">#85; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O117" s="2"/>
+      <c r="O117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CS "Přeskočit na obsah", "Otevřít / Zavřít navigaci"; DE / SK / SR translated (28 Oct).</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q117" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85</t>
+        </is>
+      </c>
       <c r="R117" s="2"/>
-      <c r="S117" s="2"/>
-      <c r="T117" s="2"/>
-      <c r="U117" s="2"/>
+      <c r="S117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
@@ -11461,17 +13748,41 @@
           <t xml:space="preserve">#83 (SKODA-1001); language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O118" s="2"/>
+      <c r="O118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">All 6 indexes 200 (CS 10, DE 5, SK 5, SR 5, SL 4) but each locale index still lists 4 chrome rows (/nav, /footer, /media-room/nav, /media-room/footer). Fix in PR #543 (open).</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" s="2"/>
-      <c r="S118" s="2"/>
-      <c r="T118" s="2"/>
-      <c r="U118" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#83 (open; fix PR #543)</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
@@ -11549,17 +13860,41 @@
           <t xml:space="preserve">#83, SKODA-1004a; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O119" s="2"/>
+      <c r="O119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/cs/tiskove-zpravy: Czech labels, 0 results – CS index has 0 press releases. CS category 4 cards OK.</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" s="2"/>
-      <c r="S119" s="2"/>
-      <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85 / SKODA-1004a</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
@@ -11635,17 +13970,37 @@
           <t xml:space="preserve">#499, #83; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O120" s="2"/>
+      <c r="O120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CS "epiq" → 2 CS stories, DE 1, SK 1; click stays on the demo (#499 suggestion part fixed). Chrome rows still suggested for "stories" (see TC-LO-004).</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q120" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#499</t>
+        </is>
+      </c>
       <c r="R120" s="2"/>
-      <c r="S120" s="2"/>
-      <c r="T120" s="2"/>
-      <c r="U120" s="2"/>
+      <c r="S120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
@@ -11724,17 +14079,37 @@
           <t xml:space="preserve">#83; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O121" s="2"/>
+      <c r="O121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Fixed since 28 Oct: CS Sportline, CS Peaq, CS Poznejte, EN counterparts, /cs/tiskove-zpravy, /cs/category → en + cs alternates; Epiq cluster en / cs / de / sk / sr. /en and /en/media-room only "en" (source lists all languages – locale homes not migrated).</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q121" s="2"/>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#83</t>
+        </is>
+      </c>
       <c r="R121" s="2"/>
-      <c r="S121" s="2"/>
-      <c r="T121" s="2"/>
-      <c r="U121" s="2"/>
+      <c r="S121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
@@ -11818,17 +14193,41 @@
           <t xml:space="preserve">#85; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O122" s="2"/>
+      <c r="O122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/cs, /de, /sk, /sr, /sl → 404 on main; source 200.</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" s="2"/>
-      <c r="S122" s="2"/>
-      <c r="T122" s="2"/>
-      <c r="U122" s="2"/>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85 (open)</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
@@ -11905,17 +14304,37 @@
           <t xml:space="preserve">#492, #85; language-switcher.md, header-megamenu.md, footer.md</t>
         </is>
       </c>
-      <c r="O123" s="2"/>
+      <c r="O123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not run: needs a DA label edit + publish (outward change, needs PO / Dev agreement). #492 not demonstrated.</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q123" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#492 (open)</t>
+        </is>
+      </c>
       <c r="R123" s="2"/>
-      <c r="S123" s="2"/>
-      <c r="T123" s="2"/>
-      <c r="U123" s="2"/>
+      <c r="S123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr" s="2">
@@ -11991,17 +14410,37 @@
           <t xml:space="preserve">SKODA-206, 802; skodapedia.md</t>
         </is>
       </c>
-      <c r="O124" s="2"/>
+      <c r="O124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">/en/skodapedia → 404 (M2, not built).</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q124" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SKODA-206 / 802 (M2)</t>
+        </is>
+      </c>
       <c r="R124" s="2"/>
-      <c r="S124" s="2"/>
-      <c r="T124" s="2"/>
-      <c r="U124" s="2"/>
+      <c r="S124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
@@ -12077,17 +14516,37 @@
           <t xml:space="preserve">SKODA-802; skodapedia.md</t>
         </is>
       </c>
-      <c r="O125" s="2"/>
+      <c r="O125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not built (M2).</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q125" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SKODA-802 (M2)</t>
+        </is>
+      </c>
       <c r="R125" s="2"/>
-      <c r="S125" s="2"/>
-      <c r="T125" s="2"/>
-      <c r="U125" s="2"/>
+      <c r="S125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
@@ -12163,17 +14622,37 @@
           <t xml:space="preserve">SKODA-210; custom-microsite.md</t>
         </is>
       </c>
-      <c r="O126" s="2"/>
+      <c r="O126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No microsite delivered (deferred).</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="Q126" s="2"/>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SKODA-210 (deferred)</t>
+        </is>
+      </c>
       <c r="R126" s="2"/>
-      <c r="S126" s="2"/>
-      <c r="T126" s="2"/>
-      <c r="U126" s="2"/>
+      <c r="S126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">QA – automated run (Playwright, real clicks)</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">main live (aem.live) vs source, fresh profile + cache-buster</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U126"/>
@@ -13708,21 +16187,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Issue</t>
+          <t xml:space="preserve">Defect ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
@@ -13737,184 +16222,380 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Summary</t>
+          <t xml:space="preserve">Test case(s)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Title</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Steps to reproduce</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Main URL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Source URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Expected</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Actual</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">GitHub status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Assign to</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#505</t>
+          <t xml:space="preserve">NEW-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Global – URLs</t>
+          <t xml:space="preserve">Faceted listing / Media Room home / Model page</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">URLs ending with "/" show "Page not found"</t>
+          <t xml:space="preserve">TC-FL-007, TC-MRH-004, TC-MD-005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/news/</t>
+          <t xml:space="preserve">Images / Videos "+" (add to media cart) cannot add anything</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/news/</t>
+          <t xml:space="preserve">1. Open Images at 1280.
+2. Hover the first card, click "+".
+3. The menu shows only "1920px" and it is disabled (aria-disabled="true").
+4. Repeat on Videos and on the Media Room Images rail: nothing is added, the cart badge stays empty, /en/media-cart shows "0 / 80 files".
+5. Compare: "+" in a story Media Box adds the file (badge 1).</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/images
+https://main--demo--skoda-storyboard.aem.live/en/videos
+https://main--demo--skoda-storyboard.aem.live/en/media-room</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/images/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Selecting a size adds the file to the media cart (source offers Original + sizes).</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Size option disabled; nothing can be added from media-feed cards.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#506</t>
+          <t xml:space="preserve">NEW-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Story detail</t>
+          <t xml:space="preserve">Global shell – Media Room menu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Slavia story: Related Stories band missing (−354px)</t>
+          <t xml:space="preserve">TC-GL-010</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/skoda-world/the-new-skoda-slavia-features-a-refreshed-look-and-an-exclusive-colour</t>
+          <t xml:space="preserve">Company › Brand Group CORE (BGC) opens the source although the page is live on the demo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/skoda-world/the-new-skoda-slavia-features-a-refreshed-look-and-an-exclusive-colour/</t>
+          <t xml:space="preserve">1. Open the Media Room home.
+2. Hover "Company" and click "Brand Group CORE (BGC)".
+3. The source page opens in a new tab.
+4. Open https://main--demo--skoda-storyboard.aem.live/en/brand-group-core-bgc – it is 200 on the demo.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/media-room</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/media-room/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Menu link opens /en/brand-group-core-bgc on the demo, same tab.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Absolute link to www.skoda-storyboard.com, new tab.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#507</t>
+          <t xml:space="preserve">NEW-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Story detail</t>
+          <t xml:space="preserve">Press kit hub</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Explore more teaser titles h3 (source h2), 19 stories</t>
+          <t xml:space="preserve">TC-PK-001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/skoda-epiq-will-win-you-over-in-just-a-few-seconds</t>
+          <t xml:space="preserve">Epiq press kit hub: "Škoda Epiq Sportline" tile missing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/skoda-epiq-will-win-you-over-in-just-a-few-seconds/</t>
+          <t xml:space="preserve">1. Open the Epiq press kit hub on main and source.
+2. List the chapter tiles.
+3. Source: … Škoda Epiq First Edition, Škoda Epiq Sportline, Frequently Asked Questions …
+4. Main: no "Škoda Epiq Sportline" tile.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-epiq-press-kit-2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-kits/skoda-epiq-press-kit-2/</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same 14 tiles as the source.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 tiles; Sportline missing.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#508</t>
+          <t xml:space="preserve">NEW-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Story detail</t>
+          <t xml:space="preserve">Press kit hub</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sunroof story: Explore more / Tags / Media Box / Related Stories h2 (source h3)</t>
+          <t xml:space="preserve">TC-PK-002</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france</t>
+          <t xml:space="preserve">Epiq press kit ZIP download is an older package than the source</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france/</t>
+          <t xml:space="preserve">1. Open the Epiq press kit hub.
+2. Check the ZIP download link.
+3. Main: cdn…/2026/08/Skoda_Epiq_c5a5f2fe.zip; source: cdn…/2026/10/Skoda_Epiq_f59cece2.zip.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-epiq-press-kit-2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-kits/skoda-epiq-press-kit-2/</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same (October) ZIP as the source.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">August ZIP (source updated in October).</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#295</t>
+          <t xml:space="preserve">NEW-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Story / PR Media Box</t>
+          <t xml:space="preserve">Press kit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Downloads Media Box title shows part of a 3rd line</t>
+          <t xml:space="preserve">TC-PK-003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/lifestyle/skodas-smarter-wireless-charging-goes-beyond-phones</t>
+          <t xml:space="preserve">Peaq first-glimpse press kit: Media Box band not full width</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/lifestyle/skodas-smarter-wireless-charging-goes-beyond-phones/</t>
+          <t xml:space="preserve">1. Open the page at 1440.
+2. Scroll to "Media Box".
+3. Measure the grey band: main left 96 / width 1248 (1280: 16 / 1248); source 0 / 1440.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-peaq-first-glimpse-of-skodas-new-electric-flagship</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-kits/skoda-peaq-first-glimpse-of-skodas-new-electric-flagship/</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Band edge to edge (0 + viewport width), as on stories after #493.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Band capped at 1248px.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#83</t>
+          <t xml:space="preserve">NEW-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -13924,61 +16605,125 @@
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Localization</t>
+          <t xml:space="preserve">Story detail</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nav / footer fragments in locale indexes and search; hreflang only on the Epiq cluster</t>
+          <t xml:space="preserve">TC-ST-012</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/cs/e-mobilita-cs/skoda-epiq-nove-obleka-efektni-soupravu-sportline</t>
+          <t xml:space="preserve">Peaq Tour de France (sunroof) story: Media Box tiles show no dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/cs/e-mobilita-cs/skoda-epiq-nove-obleka-efektni-soupravu-sportline/</t>
+          <t xml:space="preserve">1. Open the story.
+2. Scroll to Media Box.
+3. Source: a date on 10 / 10 tiles; main 0 / 10.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france/</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Dates on every tile.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No dates (page needs re-import / republish).</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#85</t>
+          <t xml:space="preserve">NEW-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Localization</t>
+          <t xml:space="preserve">Story detail</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CS listing 0 results; SK header subscribe missing; language homes 404</t>
+          <t xml:space="preserve">TC-ST-005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/cs/tiskove-zpravy</t>
+          <t xml:space="preserve">Story image slider: every slide cropped to 215px on mobile</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/cs/tiskove-zpravy/</t>
+          <t xml:space="preserve">1. Set the viewport to 375.
+2. Swipe through the story photo slider and measure each image height.
+3. Source keeps each photo ratio (182–337px); main shows every slide at 215px (20 / 20 stories).</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/practical-fun-stylish-5-reasons-to-choose-the-epiq</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/practical-fun-stylish-5-reasons-to-choose-the-epiq/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Slide height follows the image ratio.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Fixed 215px – tall photos cropped.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#420</t>
+          <t xml:space="preserve">NEW-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -13988,29 +16733,61 @@
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Global – SEO</t>
+          <t xml:space="preserve">Story detail</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Title lacks " - Škoda Storyboard"</t>
+          <t xml:space="preserve">TC-ST-009</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/images</t>
+          <t xml:space="preserve">Quote author name not bold</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/images/</t>
+          <t xml:space="preserve">1. Open the story and find the quote.
+2. Inspect the author name: main 13.33px / 400, source 16px / 600.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/meet-the-peaq-comfort-just-like-at-home
+https://main--demo--skoda-storyboard.aem.live/en/lifestyle/from-unwanted-graffiti-to-bold-support-for-womens-cycling</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/meet-the-peaq-comfort-just-like-at-home/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">16px / 600 as source.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13.33px / 400.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#76</t>
+          <t xml:space="preserve">NEW-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -14020,125 +16797,821 @@
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Branded 404</t>
+          <t xml:space="preserve">Model page</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Branded 404 variants not shown; %20 URL plain 404</t>
+          <t xml:space="preserve">TC-MD-004</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/does-not-exist</t>
+          <t xml:space="preserve">Superb model page: rails have fewer cards and a video is missing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/does-not-exist/</t>
+          <t xml:space="preserve">1. Open the Superb model page.
+2. Click Next to the end of News and Press Kits.
+3. Main 8 / 7 cards, source 10 / 10.
+4. Videos: "Škoda Superb Sportline | Footage 9:16" only on the source.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/skoda-model/new-superb</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/skoda-model/new-superb/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same cards as the source.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">News 8, Press Kits 7, one video missing.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#274</t>
+          <t xml:space="preserve">NEW-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press release</t>
+          <t xml:space="preserve">Press kit chapter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDF card icon differs (48px grey vs 64×52 white)</t>
+          <t xml:space="preserve">TC-PK-004</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-releases/skoda-auto-klaus-zellmer-to-leave-the-company</t>
+          <t xml:space="preserve">Press kit chapters missing content (Technical data, FAQ)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-releases/skoda-auto-klaus-zellmer-to-leave-the-company/</t>
+          <t xml:space="preserve">1. Open the Peaq Technical data chapter: main 1694px, 2 headings, 1 image; source 1823px, 5 headings, 4 images.
+2. Open the Epiq FAQ chapter: main 1606px, 7 headings, 0 images; source 1875px, 10 headings, 3 images.
+3. Compare the sections one by one.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-peaq-press-kit-2/technical-data
+https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-epiq-press-kit-2/frequently-asked-questions</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-kits/skoda-peaq-press-kit-2/technical-data/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same sections and images as the source.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Sections / images missing (technical data: SKODA-852, PR #546 open).</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">#342 / #447</t>
+          <t xml:space="preserve">NEW-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Home / listings</t>
+          <t xml:space="preserve">Series directory</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Content freshness: feed / index newest 15–20 Oct vs source 27 Oct</t>
+          <t xml:space="preserve">TC-SE-001</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/images</t>
+          <t xml:space="preserve">Series directory shows an extra "Explorers of sustainability" card</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/images/</t>
+          <t xml:space="preserve">1. Open the Series directory on main and source.
+2. Count the series cards: main 25, source 24.
+3. "Explorers of sustainability" is only on main (+30px).</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/series-2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/series-2/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same 24 cards as the source.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Extra card on main.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not raised</t>
+          <t xml:space="preserve">NEW-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Category listing</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-CT-004</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Lifestyle › Adventures: 2 newest 2026 stories not migrated</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open the sub-category on main and source.
+2. Source first cards: "Sand, heat, and camels…" (17. 3. 2026), "Giant spa towers, gingerbread…" (5. 2. 2026).
+3. Main starts with "A journey you will never forget" (2. 12. 2025).</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/category/lifestyle/adventures</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/category/lifestyle/adventures/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Same stories as the source (or PO-approved scope).</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2 stories not in the demo index.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not raised yet</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">vijayr-adobe</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Issue</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Priority</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Template / Area</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Summary</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Main URL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Source URL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">GitHub status (29 Oct)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Retest result (29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#505</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Global – URLs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">URLs ending with "/" show "Page not found"</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/news/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/news/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open (vijayr-adobe)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing – /en/, /en/news/, /en/skoda-model/epiq/ 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#506</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story detail</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Slavia story: Related Stories band missing (−354px)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/skoda-world/the-new-skoda-slavia-features-a-refreshed-look-and-an-exclusive-colour</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/skoda-world/the-new-skoda-slavia-features-a-refreshed-look-and-an-exclusive-colour/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open (vijayr-adobe)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#507</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story detail</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Explore more teaser titles h3 (source h2), 19 stories</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/skoda-epiq-will-win-you-over-in-just-a-few-seconds</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/skoda-epiq-will-win-you-over-in-just-a-few-seconds/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open; fix PR #548 open (not merged)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing on main</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#508</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story detail</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Sunroof story section headings h2 (source h3)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open (vijayr-adobe)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#295</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story / PR Media Box</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Downloads Media Box title shows part of a 3rd line</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/lifestyle/skodas-smarter-wireless-charging-goes-beyond-phones</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/lifestyle/skodas-smarter-wireless-charging-goes-beyond-phones/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open (reopened)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not re-measured today; no fix merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#83</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Localization</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Chrome fragments in locale indexes / search; hreflang</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/cs/query-index.json</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open; chrome fix PR #543 open</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">hreflang FIXED (en + cs on CS pages); chrome rows still in all 5 locale indexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#85</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Localization</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CS listing 0 results; SK subscribe missing; language homes 404</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/cs/tiskove-zpravy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/cs/tiskove-zpravy/</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open; SK fix in PR #543 open</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing (all 3 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#410</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Global – header</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Header at 1080: source wraps to 172px, main 108px</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still different (108 vs 172)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#420</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Global – SEO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Title lacks " - Škoda Storyboard"</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/images</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/images/</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing (all templates)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#76</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branded 404</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Branded 404 variants not shown on live; %20 plain 404</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/does-not-exist</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/does-not-exist/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Closed (completed)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAILING on live – fragments 200 on preview, 404 on live → reopen / publish</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#274</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Press release</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PDF card icon differs (48px grey vs 64×52 white)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-releases/skoda-auto-klaus-zellmer-to-leave-the-company</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-releases/skoda-auto-klaus-zellmer-to-leave-the-company/</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Closed (completed)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Difference still seen 27–28 Oct, no code change since → confirm by eye, reopen if confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">#342 / #447</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press kit</t>
+          <t xml:space="preserve">Home / listings</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Epiq press kit: "Škoda Epiq Sportline" tile missing</t>
+          <t xml:space="preserve">Content freshness: feed / index newest 15–20 Oct vs source 29 Oct</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-epiq-press-kit-2</t>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/images</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-kits/skoda-epiq-press-kit-2/</t>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/images/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Still failing (build b-b8b032bbe7)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not raised</t>
+          <t xml:space="preserve">#499</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -14148,150 +17621,116 @@
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press kit</t>
+          <t xml:space="preserve">Localization – search</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">First-glimpse press kit Media Box band 1248px (not full width)</t>
+          <t xml:space="preserve">Localized suggestions sent CS stories to the source</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/press-kits/skoda-peaq-first-glimpse-of-skodas-new-electric-flagship</t>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/cs/e-mobilita-cs/skoda-epiq-si-vas-ziska-za-par-sekund</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/press-kits/skoda-peaq-first-glimpse-of-skodas-new-electric-flagship/</t>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/cs/e-mobilita-cs/skoda-epiq-si-vas-ziska-za-par-sekund/</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PASS – suggestions stay on the demo (can be closed)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not raised</t>
+          <t xml:space="preserve">#492</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Story detail</t>
+          <t xml:space="preserve">Localization – authoring</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sunroof story Media Box dates 0/10</t>
+          <t xml:space="preserve">DA-managed per-locale UI labels</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france</t>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/cs/placeholders.json</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/a-custom-made-sunroof-walkie-talkies-and-champagne-the-skoda-peaq-at-the-tour-de-france/</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not tested (needs DA edit)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not raised</t>
+          <t xml:space="preserve">SKODA-804</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Story detail</t>
+          <t xml:space="preserve">Global – consent</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gallery slides fixed 215px at 375 (source keeps ratio)</t>
+          <t xml:space="preserve">OneTrust CMP not integrated (stub declines by default)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/practical-fun-stylish-5-reasons-to-choose-the-epiq</t>
+          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/practical-fun-stylish-5-reasons-to-choose-the-epiq/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Not raised</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Story detail</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Quote author name 13.3px/400 (source 16px/600)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/emobility/meet-the-peaq-comfort-just-like-at-home</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/emobility/meet-the-peaq-comfort-just-like-at-home/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Not raised</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Model page</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Superb rails: News 8 vs 10, Press Kits 7 vs 10; Sportline Footage 9:16 video missing</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">https://main--demo--skoda-storyboard.aem.live/en/skoda-model/new-superb</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">https://www.skoda-storyboard.com/en/skoda-model/new-superb/</t>
+          <t xml:space="preserve">https://www.skoda-storyboard.com/en/</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Planned (M2)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No cookie banner on main – TC-GL-021 Blocked</t>
         </is>
       </c>
     </row>
